--- a/docs/lem/files/xslope_baker_clay.xlsx
+++ b/docs/lem/files/xslope_baker_clay.xlsx
@@ -5691,7 +5691,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>clay (power)</t>
+          <t>compacted clay</t>
         </is>
       </c>
       <c r="C11" s="3">
